--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>13.94465545306565</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>11.44016101563709</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>18.46184953035679</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -470,9 +456,6 @@
       </c>
       <c r="E5">
         <v>16.48764510380039</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -404,57 +404,76 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Putre</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B3">
-        <v>719792</v>
+        <v>838130</v>
       </c>
       <c r="C3">
-        <v>645900</v>
+        <v>735910</v>
       </c>
       <c r="D3">
-        <v>73892</v>
+        <v>102220</v>
       </c>
       <c r="E3">
-        <v>11.44016101563709</v>
+        <v>13.89028549686781</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Putre</t>
         </is>
       </c>
       <c r="B4">
-        <v>644468</v>
+        <v>719792</v>
       </c>
       <c r="C4">
-        <v>544030</v>
+        <v>645900</v>
       </c>
       <c r="D4">
-        <v>100438</v>
+        <v>73892</v>
       </c>
       <c r="E4">
-        <v>18.46184953035679</v>
+        <v>11.44016101563709</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>644468</v>
+      </c>
+      <c r="C5">
+        <v>544030</v>
+      </c>
+      <c r="D5">
+        <v>100438</v>
+      </c>
+      <c r="E5">
+        <v>18.46184953035679</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>General Lagos</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>604600</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>519025</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>85575</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>16.48764510380039</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_arica_y_parinacota.xlsx
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -493,20 +493,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>840000</v>
+          <t>Putre</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -515,28 +507,19 @@
           <t>Camarones</t>
         </is>
       </c>
-      <c r="B3">
-        <v>644468</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>General Lagos</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>604600</v>
+          <t>Arica</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Putre</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>719792</v>
+          <t>General Lagos</t>
+        </is>
       </c>
     </row>
   </sheetData>
